--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487035_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487035_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>14.2073</v>
+        <v>12.8093</v>
       </c>
       <c r="E2" t="n">
-        <v>8.548400000000001</v>
+        <v>7.7662</v>
       </c>
       <c r="F2" t="n">
-        <v>5.6588</v>
+        <v>5.0431</v>
       </c>
       <c r="G2" t="n">
         <v>6.3314</v>
@@ -610,13 +610,13 @@
         <v>3.0881</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6599</v>
+        <v>2.2619</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9116</v>
+        <v>1.1293</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7482</v>
+        <v>1.1326</v>
       </c>
       <c r="V2" t="n">
         <v>1.5138</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.9903</v>
+        <v>8.6248</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9473</v>
+        <v>3.207</v>
       </c>
       <c r="F3" t="n">
-        <v>5.043</v>
+        <v>5.4178</v>
       </c>
       <c r="G3" t="n">
         <v>8.162599999999999</v>
@@ -688,13 +688,13 @@
         <v>3.2811</v>
       </c>
       <c r="S3" t="n">
-        <v>0.665</v>
+        <v>1.2995</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3385</v>
+        <v>0.5982</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3265</v>
+        <v>0.7013</v>
       </c>
       <c r="V3" t="n">
         <v>0.8999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5743</v>
+        <v>5.0086</v>
       </c>
       <c r="E4" t="n">
-        <v>3.802</v>
+        <v>3.8615</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7723</v>
+        <v>1.1471</v>
       </c>
       <c r="G4" t="n">
         <v>6.2897</v>
@@ -766,13 +766,13 @@
         <v>1.7371</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.152</v>
+        <v>0.2822</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2657</v>
+        <v>0.3252</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4178</v>
+        <v>-0.043</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9843</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6603</v>
+        <v>4.4079</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2276</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4327</v>
+        <v>3.6201</v>
       </c>
       <c r="G5" t="n">
         <v>2.4195</v>
@@ -844,13 +844,13 @@
         <v>3.0881</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4964</v>
+        <v>1.244</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0278</v>
+        <v>0.588</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4686</v>
+        <v>0.656</v>
       </c>
       <c r="V5" t="n">
         <v>-1.1857</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. SAINSBURY GARCIA</t>
+          <t>A. PEREZ PEREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5994</v>
+        <v>1.9154</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.7389</v>
+        <v>-1.4325</v>
       </c>
       <c r="F6" t="n">
-        <v>5.3384</v>
+        <v>3.3479</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0123</v>
+        <v>0.9326</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7049</v>
+        <v>1.1375</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3074</v>
+        <v>-0.2049</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6434</v>
+        <v>0.0243</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0157</v>
+        <v>0.6105</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6591</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>1.3689</v>
+        <v>0.9083</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7206</v>
+        <v>0.527</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6483</v>
+        <v>0.3813</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.5091</v>
+        <v>-0.579</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.8252</v>
+        <v>-2.3161</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3161</v>
+        <v>1.7371</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3822</v>
+        <v>0.662</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4429</v>
+        <v>0.2876</v>
       </c>
       <c r="U6" t="n">
-        <v>1.9393</v>
+        <v>0.3744</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2859</v>
+        <v>0.8999</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2859</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. PEREZ PEREZ</t>
+          <t>E. BONILLA HERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5158</v>
+        <v>1.2628</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7518</v>
+        <v>-0.626</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2676</v>
+        <v>1.8888</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9326</v>
+        <v>1.4695</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1375</v>
+        <v>1.4874</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2049</v>
+        <v>-0.0179</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0243</v>
+        <v>0.4014</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6105</v>
+        <v>1.6145</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-1.2131</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9083</v>
+        <v>1.0681</v>
       </c>
       <c r="N7" t="n">
-        <v>0.527</v>
+        <v>-0.1272</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3813</v>
+        <v>1.1953</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.579</v>
+        <v>0.965</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3161</v>
+        <v>-1.158</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7371</v>
+        <v>2.1231</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2624</v>
+        <v>0.3421</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0317</v>
+        <v>0.4587</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2941</v>
+        <v>-0.1167</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8999</v>
+        <v>-1.5138</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5717</v>
+        <v>-0.3281</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3281</v>
+        <v>-1.1857</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. FERRANDEZ FERNANDEZ</t>
+          <t>D. SAINSBURY GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.366</v>
+        <v>0.7488</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1449</v>
+        <v>-3.6795</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5109</v>
+        <v>4.4282</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2411</v>
+        <v>2.0123</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1076</v>
+        <v>0.7049</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1335</v>
+        <v>1.3074</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0259</v>
+        <v>0.6434</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0259</v>
+        <v>-0.0157</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.6591</v>
       </c>
       <c r="M8" t="n">
-        <v>0.267</v>
+        <v>1.3689</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1335</v>
+        <v>0.7206</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1335</v>
+        <v>0.6483</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-2.5091</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-4.8252</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.3161</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1249</v>
+        <v>1.5315</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.119</v>
+        <v>0.5024</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2439</v>
+        <v>1.0291</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. BONILLA HERNANDEZ</t>
+          <t>J. FERRANDEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3477</v>
+        <v>0.2857</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.086</v>
+        <v>-0.1449</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4337</v>
+        <v>0.4306</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4695</v>
+        <v>0.2411</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4874</v>
+        <v>0.1076</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0179</v>
+        <v>0.1335</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4014</v>
+        <v>-0.0259</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6145</v>
+        <v>-0.0259</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2131</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.0681</v>
+        <v>0.267</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1272</v>
+        <v>0.1335</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1953</v>
+        <v>0.1335</v>
       </c>
       <c r="P9" t="n">
-        <v>0.965</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.158</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1231</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5731000000000001</v>
+        <v>0.0446</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0013</v>
+        <v>-0.119</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5718</v>
+        <v>0.1636</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3281</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5162</v>
+        <v>-0.3824</v>
       </c>
       <c r="E10" t="n">
         <v>-0.3576</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1586</v>
+        <v>-0.0247</v>
       </c>
       <c r="G10" t="n">
         <v>1.647</v>
@@ -1234,13 +1234,13 @@
         <v>0.193</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1633</v>
+        <v>-0.0294</v>
       </c>
       <c r="T10" t="n">
         <v>-0.1785</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0152</v>
+        <v>0.149</v>
       </c>
       <c r="V10" t="n">
         <v>-1.228</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.452</v>
+        <v>-3.7931</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4947</v>
+        <v>-4.8358</v>
       </c>
       <c r="F11" t="n">
         <v>1.0427</v>
@@ -1312,10 +1312,10 @@
         <v>0.772</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6544</v>
+        <v>0.3133</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4442</v>
+        <v>0.1031</v>
       </c>
       <c r="U11" t="n">
         <v>0.2102</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>30.2929</v>
+        <v>30.8878</v>
       </c>
       <c r="E12" t="n">
-        <v>3.951400000000001</v>
+        <v>4.546200000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>26.3415</v>
+        <v>26.3416</v>
       </c>
       <c r="G12" t="n">
         <v>29.9085</v>
@@ -1378,7 +1378,7 @@
         <v>2.8011</v>
       </c>
       <c r="O12" t="n">
-        <v>7.247299999999999</v>
+        <v>7.247300000000001</v>
       </c>
       <c r="P12" t="n">
         <v>-3.8601</v>
@@ -1390,13 +1390,13 @@
         <v>18.3357</v>
       </c>
       <c r="S12" t="n">
-        <v>7.356800000000001</v>
+        <v>7.9517</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1002</v>
+        <v>3.694999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>4.256400000000001</v>
+        <v>4.256500000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-3.1121</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.0719</v>
+        <v>4.5375</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0276</v>
+        <v>2.2265</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0443</v>
+        <v>2.311</v>
       </c>
       <c r="G13" t="n">
         <v>1.1322</v>
@@ -1468,13 +1468,13 @@
         <v>2.8951</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2605</v>
+        <v>0.7261</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.1309</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3285</v>
+        <v>0.5952</v>
       </c>
       <c r="V13" t="n">
         <v>0.9421</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7979</v>
+        <v>3.2002</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0962</v>
+        <v>2.697</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2983</v>
+        <v>0.5031</v>
       </c>
       <c r="G14" t="n">
         <v>1.4312</v>
@@ -1546,13 +1546,13 @@
         <v>2.1231</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0193</v>
+        <v>-0.617</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4872</v>
+        <v>-0.8863</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5321</v>
+        <v>0.2693</v>
       </c>
       <c r="V14" t="n">
         <v>1.228</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.1004</v>
+        <v>-1.9805</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2432</v>
+        <v>-0.0429</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8572</v>
+        <v>-1.9376</v>
       </c>
       <c r="G15" t="n">
         <v>-1.4606</v>
@@ -1624,13 +1624,13 @@
         <v>0.193</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2611</v>
+        <v>-0.1411</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.238</v>
+        <v>-0.0377</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0231</v>
+        <v>-0.1035</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5717</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.2738</v>
+        <v>-3.1201</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7467</v>
+        <v>-0.6465</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.5271</v>
+        <v>-2.4735</v>
       </c>
       <c r="G16" t="n">
         <v>-2.5186</v>
@@ -1702,13 +1702,13 @@
         <v>0.193</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4693</v>
+        <v>-0.3156</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.238</v>
+        <v>-0.1378</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2313</v>
+        <v>-0.1778</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2859</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DINIS</t>
+          <t>D. BARROSO VALVERDE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.3768</v>
+        <v>-3.2821</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.0226</v>
+        <v>-3.5121</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3542</v>
+        <v>0.23</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.5841</v>
+        <v>-3.4907</v>
       </c>
       <c r="H17" t="n">
-        <v>-4.0893</v>
+        <v>-1.5629</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4948</v>
+        <v>-1.9278</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.6069</v>
+        <v>-2.289</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.0042</v>
+        <v>-0.3676</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6026</v>
+        <v>-1.9214</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.9773</v>
+        <v>-1.2018</v>
       </c>
       <c r="N17" t="n">
-        <v>-3.0851</v>
+        <v>-1.1953</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1078</v>
+        <v>-0.0064</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5441</v>
+        <v>0.965</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1231</v>
+        <v>-1.158</v>
       </c>
       <c r="R17" t="n">
-        <v>3.6672</v>
+        <v>2.1231</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0509</v>
+        <v>-0.1424</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7073</v>
+        <v>-0.351</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7582</v>
+        <v>0.2085</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2859</v>
+        <v>-0.614</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2859</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MARCOS SÁNCHEZ</t>
+          <t>A. DINIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.1589</v>
+        <v>-3.7033</v>
       </c>
       <c r="E18" t="n">
-        <v>-5.9955</v>
+        <v>-4.1242</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8366</v>
+        <v>0.4208</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.1894</v>
+        <v>-4.5841</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.5533</v>
+        <v>-4.0893</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.6361</v>
+        <v>-0.4948</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.8407</v>
+        <v>-1.6069</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.211</v>
+        <v>-1.0042</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.6297</v>
+        <v>-0.6026</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3487</v>
+        <v>-2.9773</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3423</v>
+        <v>-3.0851</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0064</v>
+        <v>0.1078</v>
       </c>
       <c r="P18" t="n">
-        <v>0.772</v>
+        <v>1.5441</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9301</v>
+        <v>-2.1231</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7021</v>
+        <v>3.6672</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2584</v>
+        <v>-0.3774</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2247</v>
+        <v>-0.3942</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4832</v>
+        <v>0.0168</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. BARROSO VALVERDE</t>
+          <t>A. MARCOS SÁNCHEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.1768</v>
+        <v>-4.3734</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.113</v>
+        <v>-5.9955</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0638</v>
+        <v>1.6221</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.4907</v>
+        <v>-5.1894</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5629</v>
+        <v>-2.5533</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9278</v>
+        <v>-2.6361</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.289</v>
+        <v>-3.8407</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3676</v>
+        <v>-1.211</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.9214</v>
+        <v>-2.6297</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2018</v>
+        <v>-1.3487</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1953</v>
+        <v>-1.3423</v>
       </c>
       <c r="O19" t="n">
         <v>-0.0064</v>
       </c>
       <c r="P19" t="n">
-        <v>0.965</v>
+        <v>0.772</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.158</v>
+        <v>-1.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1231</v>
+        <v>2.7021</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0371</v>
+        <v>0.044</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9518</v>
+        <v>-0.2247</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0853</v>
+        <v>0.2687</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DIEYE</t>
+          <t>J. DOSS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.3938</v>
+        <v>-4.6286</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1291</v>
+        <v>-5.5589</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2647</v>
+        <v>0.9303</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.4558</v>
+        <v>-6.7097</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0492</v>
+        <v>-6.3869</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4066</v>
+        <v>-0.3227</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.166</v>
+        <v>-3.9259</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0878</v>
+        <v>-3.7625</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2538</v>
+        <v>-0.1635</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2898</v>
+        <v>-2.7837</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.137</v>
+        <v>-2.6245</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1528</v>
+        <v>-0.1592</v>
       </c>
       <c r="P20" t="n">
-        <v>0.193</v>
+        <v>-0.965</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9301</v>
+        <v>-4.8252</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1231</v>
+        <v>3.8602</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9452</v>
+        <v>-0.8814</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.033</v>
+        <v>-0.7353</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9122</v>
+        <v>-0.1461</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1857</v>
+        <v>3.9275</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.9275</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. DOSS</t>
+          <t>A. DIEYE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.7433</v>
+        <v>-5.2735</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.0596</v>
+        <v>-3.7299</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3163</v>
+        <v>-1.5435</v>
       </c>
       <c r="G21" t="n">
-        <v>-6.7097</v>
+        <v>-3.4558</v>
       </c>
       <c r="H21" t="n">
-        <v>-6.3869</v>
+        <v>-2.0492</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3227</v>
+        <v>-1.4066</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.9259</v>
+        <v>-1.166</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.7625</v>
+        <v>0.0878</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1635</v>
+        <v>-1.2538</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.7837</v>
+        <v>-2.2898</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.6245</v>
+        <v>-2.137</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1592</v>
+        <v>-0.1528</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.965</v>
+        <v>0.193</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.8252</v>
+        <v>-1.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>3.8602</v>
+        <v>2.1231</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.9962</v>
+        <v>-0.8249</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.236</v>
+        <v>-0.6339</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7602</v>
+        <v>-0.191</v>
       </c>
       <c r="V21" t="n">
-        <v>3.9275</v>
+        <v>-1.1857</v>
       </c>
       <c r="W21" t="n">
-        <v>3.9275</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.1857</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.9389</v>
+        <v>-7.6635</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.1557</v>
+        <v>-7.655</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7832</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>-5.0629</v>
@@ -2170,13 +2170,13 @@
         <v>2.3161</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.0966</v>
+        <v>-0.8213</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4872</v>
+        <v>-0.9865</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6095</v>
+        <v>0.1652</v>
       </c>
       <c r="V22" t="n">
         <v>-0.0422</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-30.2929</v>
+        <v>-26.2873</v>
       </c>
       <c r="E23" t="n">
-        <v>-26.3416</v>
+        <v>-26.3415</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.9513</v>
+        <v>0.05419999999999931</v>
       </c>
       <c r="G23" t="n">
         <v>-29.9084</v>
@@ -2227,7 +2227,7 @@
         <v>-2.8011</v>
       </c>
       <c r="L23" t="n">
-        <v>-7.247100000000001</v>
+        <v>-7.2471</v>
       </c>
       <c r="M23" t="n">
         <v>-19.8603</v>
@@ -2239,7 +2239,7 @@
         <v>-0.8283</v>
       </c>
       <c r="P23" t="n">
-        <v>3.860100000000001</v>
+        <v>3.8601</v>
       </c>
       <c r="Q23" t="n">
         <v>-18.3357</v>
@@ -2248,13 +2248,13 @@
         <v>22.196</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.3568</v>
+        <v>-3.351</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.256600000000001</v>
+        <v>-4.2565</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.1002</v>
+        <v>0.9053</v>
       </c>
       <c r="V23" t="n">
         <v>3.112200000000001</v>
